--- a/testrails-reports-example/blusky-bug-report-26.03.2025.xlsx
+++ b/testrails-reports-example/blusky-bug-report-26.03.2025.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t xml:space="preserve">Информация</t>
   </si>
@@ -106,7 +106,10 @@
     <t xml:space="preserve">Средняя</t>
   </si>
   <si>
-    <t xml:space="preserve">Требует возможности создания поста после подтверждения email</t>
+    <t xml:space="preserve">Требует возможности создания поста после подтверждения email по ссылке</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://drive.google.com/file/d/1OGWR5KZ82WmMxtVOC41g3YKS14jIWMsC/view?usp=sharing</t>
   </si>
   <si>
     <t xml:space="preserve">26.03.2025</t>
@@ -158,7 +161,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -197,6 +200,13 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -267,7 +277,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -306,6 +316,10 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -386,7 +400,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AN10"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.42"/>
@@ -399,8 +413,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="27.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="28.06"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="18.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="60.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="19.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="66.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="70.31"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="40" min="14" style="1" width="11.52"/>
   </cols>
   <sheetData>
@@ -536,9 +550,11 @@
       <c r="L6" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="M6" s="8"/>
+      <c r="M6" s="10" t="s">
+        <v>29</v>
+      </c>
       <c r="N6" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -547,7 +563,7 @@
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
@@ -565,7 +581,7 @@
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
@@ -583,7 +599,7 @@
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
@@ -595,13 +611,13 @@
       <c r="M9" s="8"/>
       <c r="N9" s="8"/>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="101.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
@@ -630,6 +646,9 @@
     <mergeCell ref="M6:M10"/>
     <mergeCell ref="N6:N10"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="M6" r:id="rId1" display="https://drive.google.com/file/d/1OGWR5KZ82WmMxtVOC41g3YKS14jIWMsC/view?usp=sharing"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
